--- a/data/DU-SMPP.xlsx
+++ b/data/DU-SMPP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/olivier/SSDS/enseignement/UFR STAPS/Direction/Outils/celcatreport/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AF1CCD-D927-054B-812E-670152F04AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98BC9B4-51CB-C545-9867-217A534160F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="34200" windowHeight="19100" xr2:uid="{154AE90F-D41B-8B49-BA91-D855BEB6F170}"/>
   </bookViews>
